--- a/data/processed/harmonization/Physical__Clay_content/10.15485_2438579/10.15485_2438579_soil_Physical__Clay_content.xlsx
+++ b/data/processed/harmonization/Physical__Clay_content/10.15485_2438579/10.15485_2438579_soil_Physical__Clay_content.xlsx
@@ -432,7 +432,7 @@
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="31" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
@@ -4262,12 +4262,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>-112.26182</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>location.X</t>
+          <t>site.id</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4310,12 +4310,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>-112.40672</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>location.X</t>
+          <t>site.id</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4358,12 +4358,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>-112.49158</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>location.X</t>
+          <t>site.id</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>-112.38884</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>location.X</t>
+          <t>site.id</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4454,12 +4454,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>-112.4768</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>location.X</t>
+          <t>site.id</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>-112.41309</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>location.X</t>
+          <t>site.id</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
